--- a/data/trans_bre/IP13-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP13-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 4,8</t>
+          <t>-5,73; 5,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 5,67</t>
+          <t>-5,17; 5,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 7,37</t>
+          <t>-1,1; 7,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 8,54</t>
+          <t>-5,57; 8,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 117,3</t>
+          <t>-59,26; 122,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,97; 105,67</t>
+          <t>-49,69; 108,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 331,36</t>
+          <t>-24,16; 384,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-78,29; 386,73</t>
+          <t>-66,51; 382,62</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-1,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-28,37%</t>
+          <t>-25,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,49</t>
+          <t>-3,1; 2,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 0,99</t>
+          <t>-6,14; 1,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,67</t>
+          <t>-1,11; 5,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 1,97</t>
+          <t>-6,53; 2,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 81,09</t>
+          <t>-51,98; 85,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 21,1</t>
+          <t>-66,53; 30,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 179,17</t>
+          <t>-19,27; 188,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 34,44</t>
+          <t>-64,64; 44,43</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>-1,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-17,45%</t>
+          <t>-23,47%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,29</t>
+          <t>-8,06; 0,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,48</t>
+          <t>-2,59; 4,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,88</t>
+          <t>-4,66; 2,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 3,08</t>
+          <t>-6,71; 2,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-87,4; 21,77</t>
+          <t>-88,07; 35,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 336,32</t>
+          <t>-60,44; 335,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-67,77; 116,84</t>
+          <t>-66,24; 82,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 64,09</t>
+          <t>-62,32; 54,09</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 4,07</t>
+          <t>-1,74; 4,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,23</t>
+          <t>-4,94; 3,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,96</t>
+          <t>-4,01; 3,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 3,27</t>
+          <t>-2,74; 4,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,61; 223,14</t>
+          <t>-46,41; 214,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,98; 90,15</t>
+          <t>-61,42; 82,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,41; 146,54</t>
+          <t>-73,05; 167,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 96,13</t>
+          <t>-41,91; 111,1</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-11,53%</t>
+          <t>-10,25%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,5</t>
+          <t>-2,21; 1,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,51</t>
+          <t>-2,57; 1,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,77</t>
+          <t>-0,82; 2,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,56</t>
+          <t>-2,79; 1,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 36,7</t>
+          <t>-38,22; 31,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 29,79</t>
+          <t>-36,97; 31,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 78,47</t>
+          <t>-17,21; 74,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 29,18</t>
+          <t>-36,81; 32,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP13-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP13-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.1266122473558007</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.3410128511052796</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.247641404640835</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.009293445745776</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.01784513046887881</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.0417904420500075</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.8083798398139207</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1771177696494749</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,73; 5,09</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,17; 5,5</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-1,1; 7,98</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-5,57; 8,02</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-59,26; 122,78</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-49,69; 108,85</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-24,16; 384,61</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-66,51; 382,62</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.727237658797865</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.173144579340935</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.100387261948974</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.569165347190949</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5926423056525507</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4969482027108932</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2416237906279258</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6651028677495181</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.093581427933723</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.497844298741636</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.97786491889016</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.019515620665233</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.227831394445416</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.088483119374002</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3.846100953235045</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>3.82617472615345</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,38</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-5,11%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-33,18%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>53,82%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-25,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,1; 2,66</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,14; 1,23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,11; 5,79</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-6,53; 2,22</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-51,98; 85,4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-66,53; 30,3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-19,27; 188,17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-64,64; 44,43</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.2378376176476689</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.328434063105485</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.382620207469268</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.909077354495408</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.05108652836267732</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3317592241960084</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.5381936872037024</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2505339549062704</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,56</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-54,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-22,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-23,47%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.101570007127198</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.137600943872481</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.111662214218642</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-6.525849250551022</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5197722890415121</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6653095204820552</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1927409301722366</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6464020553138067</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,06; 0,53</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,59; 4,17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,66; 2,39</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,71; 2,61</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-88,07; 35,01</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-60,44; 335,72</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-66,24; 82,31</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-62,32; 54,09</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.658670024280593</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.226375916944313</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.794352122066951</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.21957482394466</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.8539590275357893</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3029655493330864</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.881710722660551</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.4443154507327142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-15,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-16,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.5648613483515</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.146236646994258</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.137775389343445</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.851443886780117</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5488948715134724</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.4128008470998565</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2214618820861792</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2347474939884854</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,74; 4,3</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,94; 3,15</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,01; 3,11</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,74; 4,12</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-46,41; 214,99</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-61,42; 82,03</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-73,05; 167,46</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-41,91; 111,1</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.062988570314658</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.592045026236893</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.663023818666911</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.707596099005624</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8807124152588556</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6044445587646899</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6623734924544673</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6231859552496259</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5330648320543714</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.174070149262386</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.392277515050142</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.614022861305057</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.3500546551033362</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3.357205188225441</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.8230510226189555</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5408943262714014</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.006637174932579</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.9453572096337286</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.6618171035031262</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.496462394628832</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3184655740060849</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1527635633548533</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1697674943038501</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.09681452275074047</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.739738397407184</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.937628164380422</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.007825703936922</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.735343102518349</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4640664990049458</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6141628859490639</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.7304634306973063</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.419091395488075</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.29713524908667</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.148014822659182</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.111181906995443</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.120162388974602</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.149851491487235</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8202604170898892</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.674574757469202</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.111038859125429</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-10,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-11,47%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-10,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,21; 1,39</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 1,56</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 2,67</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,79; 1,56</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-38,22; 31,18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-36,97; 31,39</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-17,21; 74,36</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-36,81; 32,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.5338567381889356</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.7048840110966369</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8470050451875599</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.6678565578777579</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1067871401302399</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1147433242969344</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.1918416343656075</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1024911637082304</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.205227485683008</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.572878316298493</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.8196046135442451</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.791152072450807</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3821864894552733</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3697011060122253</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1720618312356546</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3680765240228403</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.393326958762928</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.564670611426898</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.672001923249898</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.557089109063349</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.3118324419498923</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3139403295422819</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.7435611600403741</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3199894896356457</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
